--- a/2-data/treatment_and_sex_data.xlsx
+++ b/2-data/treatment_and_sex_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Jacks_WD/Spatial_learning_Monash/2-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E646FD-6618-4C43-9B64-09C8A3F43515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F6F7E8-9537-E146-956A-65734311F6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -741,7 +741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -764,7 +764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -810,7 +810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -833,7 +833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -856,7 +856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -879,7 +879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -902,7 +902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -925,7 +925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -971,7 +971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -994,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -1062,8 +1062,9 @@
       <c r="G30" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="1">
         <v>2</v>
       </c>
@@ -1086,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="1">
         <v>2</v>
       </c>
@@ -1109,7 +1110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1132,7 +1133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -1155,7 +1156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
       <c r="A35" s="1">
         <v>3</v>
       </c>
@@ -1177,8 +1178,9 @@
       <c r="G35" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1">
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1">
       <c r="A36" s="1">
         <v>3</v>
       </c>
@@ -1201,7 +1203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1">
       <c r="A37" s="1">
         <v>3</v>
       </c>
@@ -1224,7 +1226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1">
+    <row r="38" spans="1:9" ht="15.75" customHeight="1">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1247,7 +1249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1293,7 +1295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1">
       <c r="A41" s="1">
         <v>1</v>
       </c>
@@ -1316,7 +1318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1">
       <c r="A42" s="1">
         <v>2</v>
       </c>
@@ -1339,7 +1341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -1362,7 +1364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1">
       <c r="A44" s="1">
         <v>2</v>
       </c>
@@ -1385,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="13">
+    <row r="45" spans="1:9" ht="13">
       <c r="A45" s="1">
         <v>2</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="13">
+    <row r="46" spans="1:9" ht="13">
       <c r="A46" s="1">
         <v>3</v>
       </c>
@@ -1431,7 +1433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="13">
+    <row r="47" spans="1:9" ht="13">
       <c r="A47" s="1">
         <v>3</v>
       </c>
@@ -1453,8 +1455,9 @@
       <c r="G47" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="13">
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" ht="13">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="13">
+    <row r="97" spans="1:9" ht="13">
       <c r="A97" s="1">
         <v>3</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="13">
+    <row r="98" spans="1:9" ht="13">
       <c r="A98" s="1">
         <v>1</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="13">
+    <row r="99" spans="1:9" ht="13">
       <c r="A99" s="1">
         <v>1</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="13">
+    <row r="100" spans="1:9" ht="13">
       <c r="A100" s="1">
         <v>1</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="13">
+    <row r="101" spans="1:9" ht="13">
       <c r="A101" s="1">
         <v>1</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="13">
+    <row r="102" spans="1:9" ht="13">
       <c r="A102" s="1">
         <v>2</v>
       </c>
@@ -2720,7 +2723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="13">
+    <row r="103" spans="1:9" ht="13">
       <c r="A103" s="1">
         <v>2</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="13">
+    <row r="104" spans="1:9" ht="13">
       <c r="A104" s="1">
         <v>2</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="13">
+    <row r="105" spans="1:9" ht="13">
       <c r="A105" s="1">
         <v>2</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="13">
+    <row r="106" spans="1:9" ht="13">
       <c r="A106" s="1">
         <v>3</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="13">
+    <row r="107" spans="1:9" ht="13">
       <c r="A107" s="1">
         <v>3</v>
       </c>
@@ -2835,7 +2838,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="13">
+    <row r="108" spans="1:9" ht="13">
       <c r="A108" s="1">
         <v>3</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="13">
+    <row r="109" spans="1:9" ht="13">
       <c r="A109" s="1">
         <v>3</v>
       </c>
@@ -2880,8 +2883,9 @@
       <c r="G109" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="13">
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" ht="13">
       <c r="A110" s="1">
         <v>1</v>
       </c>
@@ -2904,7 +2908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="13">
+    <row r="111" spans="1:9" ht="13">
       <c r="A111" s="1">
         <v>1</v>
       </c>
@@ -2927,7 +2931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="13">
+    <row r="112" spans="1:9" ht="13">
       <c r="A112" s="1">
         <v>1</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="13">
+    <row r="113" spans="1:9" ht="13">
       <c r="A113" s="1">
         <v>1</v>
       </c>
@@ -2973,7 +2977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="13">
+    <row r="114" spans="1:9" ht="13">
       <c r="A114" s="1">
         <v>2</v>
       </c>
@@ -2996,7 +3000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="13">
+    <row r="115" spans="1:9" ht="13">
       <c r="A115" s="1">
         <v>2</v>
       </c>
@@ -3019,7 +3023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="13">
+    <row r="116" spans="1:9" ht="13">
       <c r="A116" s="1">
         <v>2</v>
       </c>
@@ -3042,7 +3046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="13">
+    <row r="117" spans="1:9" ht="13">
       <c r="A117" s="1">
         <v>2</v>
       </c>
@@ -3065,7 +3069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="13">
+    <row r="118" spans="1:9" ht="13">
       <c r="A118" s="1">
         <v>3</v>
       </c>
@@ -3088,7 +3092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="13">
+    <row r="119" spans="1:9" ht="13">
       <c r="A119" s="1">
         <v>3</v>
       </c>
@@ -3111,7 +3115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="13">
+    <row r="120" spans="1:9" ht="13">
       <c r="A120" s="1">
         <v>3</v>
       </c>
@@ -3134,7 +3138,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="13">
+    <row r="121" spans="1:9" ht="13">
       <c r="A121" s="1">
         <v>3</v>
       </c>
@@ -3157,7 +3161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="13">
+    <row r="122" spans="1:9" ht="13">
       <c r="A122" s="1">
         <v>1</v>
       </c>
@@ -3181,7 +3185,7 @@
       </c>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="13">
+    <row r="123" spans="1:9" ht="13">
       <c r="A123" s="1">
         <v>1</v>
       </c>
@@ -3205,7 +3209,7 @@
       </c>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="13">
+    <row r="124" spans="1:9" ht="13">
       <c r="A124" s="1">
         <v>1</v>
       </c>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="13">
+    <row r="125" spans="1:9" ht="13">
       <c r="A125" s="1">
         <v>1</v>
       </c>
@@ -3253,7 +3257,7 @@
       </c>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="13">
+    <row r="126" spans="1:9" ht="13">
       <c r="A126" s="1">
         <v>2</v>
       </c>
@@ -3276,8 +3280,9 @@
         <v>13</v>
       </c>
       <c r="H126" s="2"/>
-    </row>
-    <row r="127" spans="1:8" ht="13">
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:9" ht="13">
       <c r="A127" s="1">
         <v>2</v>
       </c>
@@ -3301,7 +3306,7 @@
       </c>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="13">
+    <row r="128" spans="1:9" ht="13">
       <c r="A128" s="1">
         <v>2</v>
       </c>
@@ -3444,6 +3449,7 @@
         <v>13</v>
       </c>
       <c r="H133" s="2"/>
+      <c r="I133" s="1"/>
     </row>
     <row r="134" spans="1:9" ht="13">
       <c r="A134" s="1">
@@ -4013,6 +4019,7 @@
         <v>13</v>
       </c>
       <c r="H156" s="2"/>
+      <c r="I156" s="1"/>
     </row>
     <row r="157" spans="1:9" ht="13">
       <c r="A157" s="1">
@@ -4110,7 +4117,7 @@
       </c>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="13">
+    <row r="161" spans="1:9" ht="13">
       <c r="A161" s="1">
         <v>1</v>
       </c>
@@ -4134,7 +4141,7 @@
       </c>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="13">
+    <row r="162" spans="1:9" ht="13">
       <c r="A162" s="1">
         <v>2</v>
       </c>
@@ -4157,8 +4164,9 @@
         <v>13</v>
       </c>
       <c r="H162" s="2"/>
-    </row>
-    <row r="163" spans="1:8" ht="13">
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="1:9" ht="13">
       <c r="A163" s="1">
         <v>2</v>
       </c>
@@ -4182,7 +4190,7 @@
       </c>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="13">
+    <row r="164" spans="1:9" ht="13">
       <c r="A164" s="1">
         <v>2</v>
       </c>
@@ -4206,7 +4214,7 @@
       </c>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="13">
+    <row r="165" spans="1:9" ht="13">
       <c r="A165" s="1">
         <v>2</v>
       </c>
@@ -4230,7 +4238,7 @@
       </c>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="13">
+    <row r="166" spans="1:9" ht="13">
       <c r="A166" s="1">
         <v>3</v>
       </c>
@@ -4256,7 +4264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="13">
+    <row r="167" spans="1:9" ht="13">
       <c r="A167" s="1">
         <v>3</v>
       </c>
@@ -4280,7 +4288,7 @@
       </c>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="13">
+    <row r="168" spans="1:9" ht="13">
       <c r="A168" s="1">
         <v>3</v>
       </c>
@@ -4304,7 +4312,7 @@
       </c>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="13">
+    <row r="169" spans="1:9" ht="13">
       <c r="A169" s="1">
         <v>3</v>
       </c>
@@ -4328,7 +4336,7 @@
       </c>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="13">
+    <row r="170" spans="1:9" ht="13">
       <c r="A170" s="1">
         <v>1</v>
       </c>
@@ -4352,7 +4360,7 @@
       </c>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="13">
+    <row r="171" spans="1:9" ht="13">
       <c r="A171" s="1">
         <v>1</v>
       </c>
@@ -4376,7 +4384,7 @@
       </c>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8" ht="13">
+    <row r="172" spans="1:9" ht="13">
       <c r="A172" s="1">
         <v>1</v>
       </c>
@@ -4400,7 +4408,7 @@
       </c>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="13">
+    <row r="173" spans="1:9" ht="13">
       <c r="A173" s="1">
         <v>1</v>
       </c>
@@ -4424,7 +4432,7 @@
       </c>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="1:8" ht="13">
+    <row r="174" spans="1:9" ht="13">
       <c r="A174" s="1">
         <v>2</v>
       </c>
@@ -4448,7 +4456,7 @@
       </c>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8" ht="13">
+    <row r="175" spans="1:9" ht="13">
       <c r="A175" s="1">
         <v>2</v>
       </c>
@@ -4472,7 +4480,7 @@
       </c>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="1:8" ht="13">
+    <row r="176" spans="1:9" ht="13">
       <c r="A176" s="1">
         <v>2</v>
       </c>
@@ -4496,7 +4504,7 @@
       </c>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8" ht="13">
+    <row r="177" spans="1:9" ht="13">
       <c r="A177" s="1">
         <v>2</v>
       </c>
@@ -4520,7 +4528,7 @@
       </c>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8" ht="13">
+    <row r="178" spans="1:9" ht="13">
       <c r="A178" s="1">
         <v>3</v>
       </c>
@@ -4544,7 +4552,7 @@
       </c>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8" ht="13">
+    <row r="179" spans="1:9" ht="13">
       <c r="A179" s="1">
         <v>3</v>
       </c>
@@ -4568,7 +4576,7 @@
       </c>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="1:8" ht="13">
+    <row r="180" spans="1:9" ht="13">
       <c r="A180" s="1">
         <v>3</v>
       </c>
@@ -4592,7 +4600,7 @@
       </c>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="1:8" ht="13">
+    <row r="181" spans="1:9" ht="13">
       <c r="A181" s="1">
         <v>3</v>
       </c>
@@ -4615,8 +4623,9 @@
         <v>13</v>
       </c>
       <c r="H181" s="2"/>
-    </row>
-    <row r="182" spans="1:8" ht="13">
+      <c r="I181" s="1"/>
+    </row>
+    <row r="182" spans="1:9" ht="13">
       <c r="H182" s="2"/>
     </row>
   </sheetData>
